--- a/product_surveys/020_grapes_and_grains_survey--product_surveys.xlsx
+++ b/product_surveys/020_grapes_and_grains_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -837,80 +837,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>grapes</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>favorite_beverage_choices</t>
+          <t>wine_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>grapes</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Grapes</t>
+          <t>White</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>favorite_beverage_choices</t>
+          <t>wine_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>favorite_beverage_choices</t>
+          <t>wine_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>rosé</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>Rosé</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>favorite_beverage_choices</t>
+          <t>wine_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>sparkling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>Sparkling</t>
         </is>
       </c>
     </row>
@@ -922,80 +922,80 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>fortified</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Fortified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wine_type_choices</t>
+          <t>beer_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>lager</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Lager</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wine_type_choices</t>
+          <t>beer_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rosé</t>
+          <t>ale</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Ale</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wine_type_choices</t>
+          <t>beer_type_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sparkling</t>
+          <t>ipa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>IPA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wine_type_choices</t>
+          <t>beer_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fortified</t>
+          <t>stout</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fortified</t>
+          <t>Stout</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lager</t>
+          <t>sour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lager</t>
+          <t>Sour</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ale</t>
+          <t>wheat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ale</t>
+          <t>Wheat</t>
         </is>
       </c>
     </row>
@@ -1041,80 +1041,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ipa</t>
+          <t>seltzer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Seltzer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>beer_type_choices</t>
+          <t>favorite_wine_color_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>stout</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>beer_type_choices</t>
+          <t>favorite_wine_color_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sour</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>beer_type_choices</t>
+          <t>favorite_wine_color_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wheat</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>beer_type_choices</t>
+          <t>favorite_wine_color_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>seltzer</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seltzer</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1126,197 +1126,129 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Pink</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>favorite_wine_color_choices</t>
+          <t>favorite_beer_color_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>favorite_wine_color_choices</t>
+          <t>favorite_beer_color_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>favorite_wine_color_choices</t>
+          <t>favorite_beer_color_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>amber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Amber</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>favorite_wine_color_choices</t>
+          <t>favorite_beer_color_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Gold</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>favorite_beer_color_choices</t>
+          <t>favorite_seltzer_color_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>favorite_beer_color_choices</t>
+          <t>favorite_seltzer_color_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>favorite_beer_color_choices</t>
+          <t>favorite_seltzer_color_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>amber</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>favorite_beer_color_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>favorite_seltzer_color_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>favorite_seltzer_color_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>favorite_seltzer_color_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>dark</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Dark</t>
         </is>
